--- a/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/18_operational_process_evidence.xlsx
+++ b/datasets/tenant-inputs/generated/meridian-health/standard-2026-07-v3/core-dimensions/18_operational_process_evidence.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rfc99bb9ee5b245da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R5937af5db4b94318"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="Rbc58a1450c1f49ef"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R240e0e4ded134fa5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="R649a096b79ee4526"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R3c688d3c76764d90"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" r:id="Rf5b1052e158e4a76"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Client Intake" sheetId="2" r:id="R882efb4484f244db"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questionnaire" sheetId="3" r:id="R33716d15af3d4452"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Examples" sheetId="4" r:id="R0953a145de4040ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reference Values" sheetId="5" r:id="Rc44d1be6f13444ca"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationship Expectations" sheetId="6" r:id="R48d01015449e4c54"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -628,7 +628,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06406a638e5e4ef9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf7ec56772e0f4df6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -809,7 +809,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ENTERPRISE-EV01; MERIDIAN-HEALTH-MH-ENTERPRISE-EV02</x:v>
       </x:c>
       <x:c r="O6" s="78" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Validate Executive Office evidence and readiness workflow (record 1) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for operational process evidence.</x:v>
       </x:c>
       <x:c r="P6" s="41" t="str">
         <x:v>High</x:v>
@@ -859,7 +859,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV01; MERIDIAN-HEALTH-MH-CLINICAL-OPS-EV02</x:v>
       </x:c>
       <x:c r="O7" s="79" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Confirm Provider Operations evidence and readiness workflow (record 2) current-vs-target status, module boundary, volume baseline, and relationship links before this operational process evidence record is used downstream.</x:v>
       </x:c>
       <x:c r="P7" s="45" t="str">
         <x:v>High</x:v>
@@ -909,7 +909,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV01; MERIDIAN-HEALTH-MH-CLAIMS-OPS-EV02</x:v>
       </x:c>
       <x:c r="O8" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Attach client evidence for Claims Operations evidence and readiness workflow (record 3), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P8" t="str">
         <x:v>High</x:v>
@@ -959,7 +959,7 @@
         <x:v>MERIDIAN-HEALTH-MH-ELIGIBILITY-EV01; MERIDIAN-HEALTH-MH-ELIGIBILITY-EV02</x:v>
       </x:c>
       <x:c r="O9" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Reconcile Eligibility and Benefits evidence and readiness workflow (record 4) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P9" t="str">
         <x:v>High</x:v>
@@ -1009,7 +1009,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV01; MERIDIAN-HEALTH-MH-PRIOR-AUTH-EV02</x:v>
       </x:c>
       <x:c r="O10" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Prior Authorization and UM evidence and readiness workflow (record 5) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P10" t="str">
         <x:v>High</x:v>
@@ -1047,19 +1047,19 @@
         <x:v>Known source inventory and owner context exist in candidate pack.</x:v>
       </x:c>
       <x:c r="K11" t="str">
-        <x:v>Automate evidence intake, relationship projection, data quality checks, and module context packets.</x:v>
+        <x:v>audited Claude agent-assist answer packet; Genesys-Salesforce-claims context join; human-approved next-best-action workflow.</x:v>
       </x:c>
       <x:c r="L11" t="str">
-        <x:v>Relationship depth and measured outcomes must be validated before high-stakes claims.</x:v>
+        <x:v>intent taxonomy drift; CRM-to-claims join gaps; stale knowledge article duplicates.</x:v>
       </x:c>
       <x:c r="M11" t="str">
         <x:v>Evidence lineage, privacy/security review, source approval, and operator promotion gate required.</x:v>
       </x:c>
       <x:c r="N11" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV01; MERIDIAN-HEALTH-MH-CONTACT-CENTER-EV02</x:v>
+        <x:v>Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields.; Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions.; Call transcript annotation sample for billing, eligibility, claims status, and prior authorization intents.; Knowledge article export with duplicate and stale article flags.; Member service KPI baseline for AHT, FCR, transfer rate, complaint escalation, and quality score.</x:v>
       </x:c>
       <x:c r="O11" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Validate Contact Center and Member Service evidence and readiness workflow (record 6) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P11" t="str">
         <x:v>High</x:v>
@@ -1109,7 +1109,7 @@
         <x:v>MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV01; MERIDIAN-HEALTH-MH-REVENUE-CYCLE-EV02</x:v>
       </x:c>
       <x:c r="O12" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Confirm Revenue Cycle Operations evidence and readiness workflow (record 7) current-vs-target status, module boundary, volume baseline, and relationship links before this operational process evidence record is used downstream.</x:v>
       </x:c>
       <x:c r="P12" t="str">
         <x:v>High</x:v>
@@ -1147,19 +1147,19 @@
         <x:v>Known source inventory and owner context exist in candidate pack.</x:v>
       </x:c>
       <x:c r="K13" t="str">
-        <x:v>Automate evidence intake, relationship projection, data quality checks, and module context packets.</x:v>
+        <x:v>Databricks Finance Gold certification; vendor master harmonization; cost-center hierarchy stewardship.</x:v>
       </x:c>
       <x:c r="L13" t="str">
-        <x:v>Relationship depth and measured outcomes must be validated before high-stakes claims.</x:v>
+        <x:v>inconsistent vendor spend definitions; slow close-window dashboards; incomplete lineage from ERP to BI.</x:v>
       </x:c>
       <x:c r="M13" t="str">
         <x:v>Evidence lineage, privacy/security review, source approval, and operator promotion gate required.</x:v>
       </x:c>
       <x:c r="N13" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV01; MERIDIAN-HEALTH-MH-FINANCE-ANALYTICS-EV02</x:v>
+        <x:v>Oracle ERP Finance GL/AP/AR extract as of 2026-06 synthetic close cycle.; SQL Server Finance Mart schema inventory showing GL, AP, AR, budget, vendor spend, and cost-center schemas.; Informatica finance ETL inventory with 200 nightly jobs and close-window failure notes.; Tableau and Power BI finance dashboard inventory with certified vs shadow-report split.; Finance Gold Data Product design notes for Databricks target certification.</x:v>
       </x:c>
       <x:c r="O13" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Validate Finance Analytics evidence and readiness workflow (record 8) against Finance Analytics evidence: slow close-window dashboards; confirm vendor master harmonization owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P13" t="str">
         <x:v>High</x:v>
@@ -1209,7 +1209,7 @@
         <x:v>MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV01; MERIDIAN-HEALTH-MH-HR-WORKFORCE-EV02</x:v>
       </x:c>
       <x:c r="O14" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Reconcile Workforce Analytics evidence and readiness workflow (record 9) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P14" t="str">
         <x:v>High</x:v>
@@ -1259,7 +1259,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV01; MERIDIAN-HEALTH-MH-CLINICAL-QUALITY-EV02</x:v>
       </x:c>
       <x:c r="O15" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Clinical Quality Analytics evidence and readiness workflow (record 10) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P15" t="str">
         <x:v>High</x:v>
@@ -1309,7 +1309,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV01; MERIDIAN-HEALTH-MH-CLAIMS-ANALYTICS-EV02</x:v>
       </x:c>
       <x:c r="O16" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Validate Claims and Payment Analytics evidence and readiness workflow (record 11) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for operational process evidence.</x:v>
       </x:c>
       <x:c r="P16" t="str">
         <x:v>High</x:v>
@@ -1359,7 +1359,7 @@
         <x:v>MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV01; MERIDIAN-HEALTH-MH-PROVIDER-PERFORMANCE-EV02</x:v>
       </x:c>
       <x:c r="O17" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Confirm Provider Performance Analytics evidence and readiness workflow (record 12) current-vs-target status, module boundary, volume baseline, and relationship links before this operational process evidence record is used downstream.</x:v>
       </x:c>
       <x:c r="P17" t="str">
         <x:v>High</x:v>
@@ -1409,7 +1409,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV01; MERIDIAN-HEALTH-MH-DATA-PLATFORM-EV02</x:v>
       </x:c>
       <x:c r="O18" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Attach client evidence for Enterprise Data Platform evidence and readiness workflow (record 13), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P18" t="str">
         <x:v>High</x:v>
@@ -1459,7 +1459,7 @@
         <x:v>MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV01; MERIDIAN-HEALTH-MH-DATA-GOVERNANCE-EV02</x:v>
       </x:c>
       <x:c r="O19" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Reconcile Data Governance and Data Quality evidence and readiness workflow (record 14) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P19" t="str">
         <x:v>High</x:v>
@@ -1497,19 +1497,19 @@
         <x:v>Known source inventory and owner context exist in candidate pack.</x:v>
       </x:c>
       <x:c r="K20" t="str">
-        <x:v>Automate evidence intake, relationship projection, data quality checks, and module context packets.</x:v>
+        <x:v>audited Claude agent-assist answer packet; Genesys-Salesforce-claims context join; human-approved next-best-action workflow.</x:v>
       </x:c>
       <x:c r="L20" t="str">
-        <x:v>Relationship depth and measured outcomes must be validated before high-stakes claims.</x:v>
+        <x:v>intent taxonomy drift; CRM-to-claims join gaps; stale knowledge article duplicates.</x:v>
       </x:c>
       <x:c r="M20" t="str">
         <x:v>Evidence lineage, privacy/security review, source approval, and operator promotion gate required.</x:v>
       </x:c>
       <x:c r="N20" t="str">
-        <x:v>MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV01; MERIDIAN-HEALTH-MH-AGENT-ASSIST-EV02</x:v>
+        <x:v>Genesys call sample with queue, intent, handle time, transfer flag, and after-call-work fields.; Salesforce Health Cloud case extract with member inquiry categories and resolution dispositions.; Call transcript annotation sample for billing, eligibility, claims status, and prior authorization intents.; Knowledge article export with duplicate and stale article flags.; Member service KPI baseline for AHT, FCR, transfer rate, complaint escalation, and quality score.</x:v>
       </x:c>
       <x:c r="O20" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Validate Agent Assist and Next Best Action evidence and readiness workflow (record 15) against Agent Assist / Member Service evidence: stale knowledge article duplicates; confirm human-approved next-best-action workflow owner, timing, and source lineage before active promotion.</x:v>
       </x:c>
       <x:c r="P20" t="str">
         <x:v>High</x:v>
@@ -1559,7 +1559,7 @@
         <x:v>MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV01; MERIDIAN-HEALTH-MH-UNIFIED-LAKEHOUSE-EV02</x:v>
       </x:c>
       <x:c r="O21" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Validate Unified Clinical and Claims Lakehouse evidence and readiness workflow (record 16) with the accountable owner; capture source extract date, authoritative system, and promotion-ready evidence for operational process evidence.</x:v>
       </x:c>
       <x:c r="P21" t="str">
         <x:v>High</x:v>
@@ -1609,7 +1609,7 @@
         <x:v>MERIDIAN-HEALTH-MH-IT-BUDGET-EV01; MERIDIAN-HEALTH-MH-IT-BUDGET-EV02</x:v>
       </x:c>
       <x:c r="O22" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Confirm IT Budget and Tower Baseline evidence and readiness workflow (record 17) current-vs-target status, module boundary, volume baseline, and relationship links before this operational process evidence record is used downstream.</x:v>
       </x:c>
       <x:c r="P22" t="str">
         <x:v>High</x:v>
@@ -1659,7 +1659,7 @@
         <x:v>MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV01; MERIDIAN-HEALTH-MH-VENDOR-SOURCING-EV02</x:v>
       </x:c>
       <x:c r="O23" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Attach client evidence for Vendor and Contract Optimization evidence and readiness workflow (record 18), including owner attestation, data sensitivity, refresh cadence, and unresolved data-quality caveats.</x:v>
       </x:c>
       <x:c r="P23" t="str">
         <x:v>High</x:v>
@@ -1709,7 +1709,7 @@
         <x:v>MERIDIAN-HEALTH-MH-CMDB-INFRA-EV01; MERIDIAN-HEALTH-MH-CMDB-INFRA-EV02</x:v>
       </x:c>
       <x:c r="O24" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Reconcile Infrastructure and CMDB evidence and readiness workflow (record 19) to related systems, data assets, vendors, metrics, and risks so the record does not remain a standalone inventory item.</x:v>
       </x:c>
       <x:c r="P24" t="str">
         <x:v>High</x:v>
@@ -1759,7 +1759,7 @@
         <x:v>MERIDIAN-HEALTH-MH-INCIDENTS-EV01; MERIDIAN-HEALTH-MH-INCIDENTS-EV02</x:v>
       </x:c>
       <x:c r="O25" t="str">
-        <x:v>Need actual process maps, control owners, and audit samples.</x:v>
+        <x:v>Confirm operational scale, support group, lineage, and module-readiness caveats for Incident Problem Change Operations evidence and readiness workflow (record 20) in the next SME workshop.</x:v>
       </x:c>
       <x:c r="P25" t="str">
         <x:v>High</x:v>
@@ -1777,7 +1777,7 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc5f65b9c1ce94677"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8810b4329e32419c"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1852,7 +1852,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R025c964f722240a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71ee343cbc6d4baa"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2046,7 +2046,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra46f49ca0fd24c64"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0b63b3f62b744ad1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2100,7 +2100,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R056fae216a9245f3"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R03eb50cdd3f0439a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2210,7 +2210,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R58684b01f1a442a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3f522e8aefd244df"/>
   </x:tableParts>
 </x:worksheet>
 </file>